--- a/survey_templates/044_energy_concepts_assessment--survey_templates.xlsx
+++ b/survey_templates/044_energy_concepts_assessment--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_one</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,20 +538,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>energy_knowledge</t>
+          <t>energy_attitude_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Do you think energy is important?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one of the options below.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,20 +565,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>energy_knowledge_2</t>
+          <t>energy_attitude_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How does energy affect your daily life?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select one of the options below.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -584,20 +592,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>energy_knowledge_3</t>
+          <t>energy_attitude_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Energy is an important part of our lives.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select one of the options below.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -612,15 +624,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>energy_knowledge_4</t>
+          <t>energy_knowledge_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is your understanding of energy?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please describe your understanding in 100 words.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -635,61 +651,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>energy_knowledge_5</t>
+          <t>energy_knowledge_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Energy is what?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please describe your understanding in 100 words.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>attitudes</t>
+          <t>energy_concept_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Attitudes towards energy</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Energy is renewable or non-renewable?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>attitudes_2</t>
+          <t>energy_knowledge_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>attitudes-2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is your understanding of energy efficiency?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please describe your understanding in 100 words.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -704,18 +732,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_two</t>
+          <t>energy_knowledge_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Page 2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is your understanding of energy sources?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please describe your understanding in 100 words.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +759,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_three</t>
+          <t>energy_knowledge_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is your understanding of energy conversion?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please describe your understanding in 100 words.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,15 +786,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>energy_knowledge_2</t>
+          <t>energy_knowledge_6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>energy-knowledge-2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your understanding of energy storage?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please describe your understanding in 100 words.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -768,22 +808,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>energy_knowledge</t>
+          <t>energy_concept_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Energy sources can be harnessed to generate electricity.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Describe your understanding of energy in 100 words</t>
+          <t>Select all that apply.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -800,12 +840,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page_four</t>
+          <t>page_two</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Page 4</t>
+          <t>Page 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,12 +863,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page_five</t>
+          <t>page_three</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -841,27 +881,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>energy_concepts_2</t>
+          <t>page_four</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Energy Concepts</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+          <t>Page 4</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -873,223 +909,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>energy_knowledge_6</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is your understanding of energy</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>energy_knowledge_7</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>energy_knowledge_8</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>energy_knowledge_9</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>energy_knowledge_10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>energy_knowledge_11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>energy_knowledge_12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your understanding of energy</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_six</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Page 6</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_seven</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Page 7</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1106,12 +935,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1134,102 +963,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>attitudes_choices</t>
+          <t>energy_attitude_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>attitudes_choices</t>
+          <t>energy_attitude_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>attitudes_2_choices</t>
+          <t>energy_attitude_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_much</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very much</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>attitudes_2_choices</t>
+          <t>energy_attitude_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>a_little</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A little</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>energy_concepts_2_choices</t>
+          <t>energy_attitude_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>energy_concepts_2_choices</t>
+          <t>energy_attitude_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>energy_attitude_3_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>disagree</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>energy_concept_1_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>renewable</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Renewable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>energy_concept_1_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>non-renewable</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Non-renewable</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>energy_concept_2_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>energy_concept_2_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>energy_concept_2_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>hydro</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>energy_concept_2_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
         </is>
       </c>
     </row>
